--- a/src/data/others/satellite.xlsx
+++ b/src/data/others/satellite.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\MIT Dropbox\Yen-Heng Chen\2026\2026-13_EPPAinJulia\EPPAinJulia\src\data\others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088311D2-5026-43A2-8175-E2239A94A261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C441357-D271-4694-8406-2967F4EEAE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69050F7B-07FD-47B9-AC7B-A9BBF237F6D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{69050F7B-07FD-47B9-AC7B-A9BBF237F6D0}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="1" r:id="rId1"/>
+    <sheet name="argdpgrrate" sheetId="2" r:id="rId2"/>
+    <sheet name="popa_eppa" sheetId="3" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -194,8 +196,76 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Henry</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{BC41645A-5F2E-44CD-BB76-C8FFB1A50469}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Henry:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+EPPA8 2025 numbers</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Henry</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{0F9F547E-159C-41FB-B7A8-11BF454DDC00}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Henry:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+EPPA 8 2020-2025 interpolation</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="26">
   <si>
     <t>USA</t>
   </si>
@@ -271,12 +341,18 @@
   <si>
     <t>bio_baseyear</t>
   </si>
+  <si>
+    <t>year</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,6 +372,13 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -318,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -327,6 +410,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,98 +584,7 @@
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
-      <sheetData sheetId="16">
-        <row r="28">
-          <cell r="C28">
-            <v>1.746434956928161</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="C29">
-            <v>4.9846277014075784E-2</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="C30">
-            <v>6.3851109066356067E-4</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="C31">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="C32">
-            <v>4.4479227208808836E-3</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="C33">
-            <v>1.0647518907566096</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="C34">
-            <v>6.5327848861302079E-2</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="C35">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="C36">
-            <v>8.0763372E-2</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="C37">
-            <v>7.0236219972991676E-2</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="C38">
-            <v>2.4164107143868616E-2</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="C39">
-            <v>0.88768091150899997</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="C40">
-            <v>4.057304520621155E-3</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="C41">
-            <v>6.8992749869112269E-4</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="C42">
-            <v>0.29837209689047656</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="C43">
-            <v>0.3339931407865579</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="C44">
-            <v>1.7921723003999999E-2</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="C45">
-            <v>0.11244437900094614</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
@@ -1391,58 +1385,2281 @@
       </c>
       <c r="B7" s="3">
         <f t="array" ref="B7:S7">TRANSPOSE([1]readgtap_bio!$C$28:$C$45)</f>
-        <v>1.746434956928161</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>4.9846277014075784E-2</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3">
-        <v>6.3851109066356067E-4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>4.4479227208808836E-3</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3">
-        <v>1.0647518907566096</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3">
-        <v>6.5327848861302079E-2</v>
+        <v>0</v>
       </c>
       <c r="I7" s="3">
         <v>0</v>
       </c>
       <c r="J7" s="3">
-        <v>8.0763372E-2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3">
-        <v>7.0236219972991676E-2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3">
-        <v>2.4164107143868616E-2</v>
+        <v>0</v>
       </c>
       <c r="M7" s="3">
-        <v>0.88768091150899997</v>
+        <v>0</v>
       </c>
       <c r="N7" s="3">
-        <v>4.057304520621155E-3</v>
+        <v>0</v>
       </c>
       <c r="O7" s="3">
-        <v>6.8992749869112269E-4</v>
+        <v>0</v>
       </c>
       <c r="P7" s="3">
-        <v>0.29837209689047656</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="3">
-        <v>0.3339931407865579</v>
+        <v>0</v>
       </c>
       <c r="R7" s="3">
-        <v>1.7921723003999999E-2</v>
+        <v>0</v>
       </c>
       <c r="S7" s="3">
-        <v>0.11244437900094614</v>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF41F6A-FA2C-4A28-888D-BCDFC50C8C79}">
+  <dimension ref="A1:S18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2" s="4">
+        <v>2.3682265429612447E-2</v>
+      </c>
+      <c r="C2" s="4">
+        <v>2.9724594735724114E-2</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="E2" s="4">
+        <v>8.3413431830521908E-3</v>
+      </c>
+      <c r="F2" s="4">
+        <v>2.8081103542524063E-2</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1.6708505942786653E-2</v>
+      </c>
+      <c r="H2" s="4">
+        <v>2.4E-2</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1.1000000000000001E-2</v>
+      </c>
+      <c r="J2" s="4">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="K2" s="4">
+        <v>4.2736599245274516E-2</v>
+      </c>
+      <c r="L2" s="4">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="M2" s="4">
+        <v>3.3917385064212879E-2</v>
+      </c>
+      <c r="N2" s="4">
+        <v>4.9679066361608099E-2</v>
+      </c>
+      <c r="O2" s="4">
+        <v>4.3314692360027246E-2</v>
+      </c>
+      <c r="P2" s="4">
+        <v>2.6000000000000002E-2</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>4.7E-2</v>
+      </c>
+      <c r="R2" s="4">
+        <v>1.9E-2</v>
+      </c>
+      <c r="S2" s="4">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2.3682265429612447E-2</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2.9724594735724114E-2</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="E3" s="4">
+        <v>8.3413431830521908E-3</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2.8081103542524063E-2</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1.6708505942786653E-2</v>
+      </c>
+      <c r="H3" s="4">
+        <v>2.4E-2</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1.1000000000000001E-2</v>
+      </c>
+      <c r="J3" s="4">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="K3" s="4">
+        <v>4.2736599245274516E-2</v>
+      </c>
+      <c r="L3" s="4">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="M3" s="4">
+        <v>3.3917385064212879E-2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>4.9679066361608099E-2</v>
+      </c>
+      <c r="O3" s="4">
+        <v>4.3314692360027246E-2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.6000000000000002E-2</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>4.7E-2</v>
+      </c>
+      <c r="R3" s="4">
+        <v>1.9E-2</v>
+      </c>
+      <c r="S3" s="4">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2030</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2.0608795827267226E-2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>2.7510990293483618E-2</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="E4" s="4">
+        <v>9.4845114524750897E-3</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2.5979350195200101E-2</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J4" s="4">
+        <v>3.26109697562438E-2</v>
+      </c>
+      <c r="K4" s="4">
+        <v>3.7343184569484704E-2</v>
+      </c>
+      <c r="L4" s="4">
+        <v>6.0863187303229704E-2</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="N4" s="4">
+        <v>4.4633874432133493E-2</v>
+      </c>
+      <c r="O4" s="4">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>4.5719586847235504E-2</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="S4" s="4">
+        <v>3.8239446543394201E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2035</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2.5956333331896939E-2</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1.29476787375846E-2</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2.6876120730655005E-2</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J5" s="4">
+        <v>2.7999999999999997E-2</v>
+      </c>
+      <c r="K5" s="4">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="L5" s="4">
+        <v>4.61364889804496E-2</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="N5" s="4">
+        <v>4.3672308246444101E-2</v>
+      </c>
+      <c r="O5" s="4">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>4.2990503642884599E-2</v>
+      </c>
+      <c r="R5" s="4">
+        <v>2.64219295015415E-2</v>
+      </c>
+      <c r="S5" s="4">
+        <v>3.4828339237705598E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2040</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1.8910629847405217E-2</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2.5000375615744971E-2</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1.2931432835156201E-2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2.5042758693412298E-2</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1.5459536579742502E-2</v>
+      </c>
+      <c r="J6" s="4">
+        <v>2.7000000000000003E-2</v>
+      </c>
+      <c r="K6" s="4">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="L6" s="4">
+        <v>4.6094113855748707E-2</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="N6" s="4">
+        <v>4.2091398503262899E-2</v>
+      </c>
+      <c r="O6" s="4">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>4.0266024272180595E-2</v>
+      </c>
+      <c r="R6" s="4">
+        <v>2.183054613507308E-2</v>
+      </c>
+      <c r="S6" s="4">
+        <v>3.0728174747786802E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2045</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1.8369966763721896E-2</v>
+      </c>
+      <c r="C7" s="4">
+        <v>6.7999999999999996E-3</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2.8485485056409257E-2</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1.1429975180917535E-2</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2.5209405630471901E-2</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1.3448011250824428E-2</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1.51758808751725E-2</v>
+      </c>
+      <c r="J7" s="4">
+        <v>2.427974321313258E-2</v>
+      </c>
+      <c r="K7" s="4">
+        <v>2.667658516012044E-2</v>
+      </c>
+      <c r="L7" s="4">
+        <v>3.8875518853010299E-2</v>
+      </c>
+      <c r="M7" s="4">
+        <v>2.6301070769493645E-2</v>
+      </c>
+      <c r="N7" s="4">
+        <v>3.8774451980654358E-2</v>
+      </c>
+      <c r="O7" s="4">
+        <v>3.1919691952427887E-2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>2.9104582822257644E-2</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>3.5274891320482601E-2</v>
+      </c>
+      <c r="R7" s="4">
+        <v>2.2427838979225463E-2</v>
+      </c>
+      <c r="S7" s="4">
+        <v>2.7034463919881402E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2050</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1.7932586602680899E-2</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1.9678405818512896E-2</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2.7807259221732845E-2</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1.1157832914705212E-2</v>
+      </c>
+      <c r="F8" s="4">
+        <v>2.4609181686889237E-2</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1.312782050675718E-2</v>
+      </c>
+      <c r="H8" s="4">
+        <v>2.9285714285714283E-2</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1.4814550378144583E-2</v>
+      </c>
+      <c r="J8" s="4">
+        <v>2.3701654089010375E-2</v>
+      </c>
+      <c r="K8" s="4">
+        <v>2.6041428370593762E-2</v>
+      </c>
+      <c r="L8" s="4">
+        <v>3.7949911261271958E-2</v>
+      </c>
+      <c r="M8" s="4">
+        <v>2.5674854798791415E-2</v>
+      </c>
+      <c r="N8" s="4">
+        <v>3.7851250743019732E-2</v>
+      </c>
+      <c r="O8" s="4">
+        <v>3.115969928689389E-2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>2.8411616564584845E-2</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>3.4435012955709207E-2</v>
+      </c>
+      <c r="R8" s="4">
+        <v>2.1893842813053427E-2</v>
+      </c>
+      <c r="S8" s="4">
+        <v>2.6390786207503274E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2055</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1.7495206441639901E-2</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1.7800581048343835E-2</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2.7129033387056432E-2</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1.088569064849289E-2</v>
+      </c>
+      <c r="F9" s="4">
+        <v>2.4008957743306573E-2</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1.2807629762689931E-2</v>
+      </c>
+      <c r="H9" s="4">
+        <v>2.8571428571428567E-2</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1.4453219881116666E-2</v>
+      </c>
+      <c r="J9" s="4">
+        <v>2.3123564964888169E-2</v>
+      </c>
+      <c r="K9" s="4">
+        <v>2.5406271581067084E-2</v>
+      </c>
+      <c r="L9" s="4">
+        <v>3.7024303669533618E-2</v>
+      </c>
+      <c r="M9" s="4">
+        <v>2.5048638828089186E-2</v>
+      </c>
+      <c r="N9" s="4">
+        <v>3.6928049505385106E-2</v>
+      </c>
+      <c r="O9" s="4">
+        <v>3.0399706621359893E-2</v>
+      </c>
+      <c r="P9" s="4">
+        <v>2.7718650306912045E-2</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>3.3595134590935813E-2</v>
+      </c>
+      <c r="R9" s="4">
+        <v>2.1359846646881391E-2</v>
+      </c>
+      <c r="S9" s="4">
+        <v>2.5747108495125147E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2060</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1.7057826280598903E-2</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1.6057214063759345E-2</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2.645080755238002E-2</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1.0613548382280567E-2</v>
+      </c>
+      <c r="F10" s="4">
+        <v>2.340873379972391E-2</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1.2487439018622683E-2</v>
+      </c>
+      <c r="H10" s="4">
+        <v>2.7857142857142851E-2</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1.4091889384088748E-2</v>
+      </c>
+      <c r="J10" s="4">
+        <v>2.2545475840765963E-2</v>
+      </c>
+      <c r="K10" s="4">
+        <v>2.4771114791540406E-2</v>
+      </c>
+      <c r="L10" s="4">
+        <v>3.6098696077795277E-2</v>
+      </c>
+      <c r="M10" s="4">
+        <v>2.4422422857386956E-2</v>
+      </c>
+      <c r="N10" s="4">
+        <v>3.6004848267750481E-2</v>
+      </c>
+      <c r="O10" s="4">
+        <v>2.9639713955825896E-2</v>
+      </c>
+      <c r="P10" s="4">
+        <v>2.7025684049239246E-2</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>3.2755256226162419E-2</v>
+      </c>
+      <c r="R10" s="4">
+        <v>2.0825850480709354E-2</v>
+      </c>
+      <c r="S10" s="4">
+        <v>2.5103430782747019E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2065</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1.6620446119557906E-2</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1.7414825168802946E-2</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2.5772581717703608E-2</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1.0341406116068244E-2</v>
+      </c>
+      <c r="F11" s="4">
+        <v>2.2808509856141246E-2</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1.2167248274555434E-2</v>
+      </c>
+      <c r="H11" s="4">
+        <v>2.7142857142857135E-2</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1.3730558887060831E-2</v>
+      </c>
+      <c r="J11" s="4">
+        <v>2.1967386716643757E-2</v>
+      </c>
+      <c r="K11" s="4">
+        <v>2.4135958002013728E-2</v>
+      </c>
+      <c r="L11" s="4">
+        <v>3.5173088486056936E-2</v>
+      </c>
+      <c r="M11" s="4">
+        <v>2.3796206886684726E-2</v>
+      </c>
+      <c r="N11" s="4">
+        <v>3.5081647030115855E-2</v>
+      </c>
+      <c r="O11" s="4">
+        <v>2.8879721290291899E-2</v>
+      </c>
+      <c r="P11" s="4">
+        <v>2.6332717791566446E-2</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>3.1915377861389024E-2</v>
+      </c>
+      <c r="R11" s="4">
+        <v>2.0291854314537318E-2</v>
+      </c>
+      <c r="S11" s="4">
+        <v>2.4459753070368892E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2070</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1.6183065958516908E-2</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1.7649691680436872E-2</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2.5094355883027195E-2</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1.0069263849855922E-2</v>
+      </c>
+      <c r="F12" s="4">
+        <v>2.2208285912558582E-2</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1.1847057530488186E-2</v>
+      </c>
+      <c r="H12" s="4">
+        <v>2.6428571428571419E-2</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1.3369228390032914E-2</v>
+      </c>
+      <c r="J12" s="4">
+        <v>2.1389297592521551E-2</v>
+      </c>
+      <c r="K12" s="4">
+        <v>2.3500801212487051E-2</v>
+      </c>
+      <c r="L12" s="4">
+        <v>3.4247480894318595E-2</v>
+      </c>
+      <c r="M12" s="4">
+        <v>2.3169990915982496E-2</v>
+      </c>
+      <c r="N12" s="4">
+        <v>3.4158445792481229E-2</v>
+      </c>
+      <c r="O12" s="4">
+        <v>2.8119728624757902E-2</v>
+      </c>
+      <c r="P12" s="4">
+        <v>2.5639751533893647E-2</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>3.107549949661563E-2</v>
+      </c>
+      <c r="R12" s="4">
+        <v>1.9757858148365282E-2</v>
+      </c>
+      <c r="S12" s="4">
+        <v>2.3816075357990765E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2075</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1.5745685797475911E-2</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1.6925029962986279E-2</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2.4416130048350783E-2</v>
+      </c>
+      <c r="E13" s="4">
+        <v>9.7971215836435994E-3</v>
+      </c>
+      <c r="F13" s="4">
+        <v>2.1608061968975918E-2</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1.1526866786420937E-2</v>
+      </c>
+      <c r="H13" s="4">
+        <v>2.5714285714285703E-2</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1.3007897893004997E-2</v>
+      </c>
+      <c r="J13" s="4">
+        <v>2.0811208468399345E-2</v>
+      </c>
+      <c r="K13" s="4">
+        <v>2.2865644422960373E-2</v>
+      </c>
+      <c r="L13" s="4">
+        <v>3.3321873302580254E-2</v>
+      </c>
+      <c r="M13" s="4">
+        <v>2.2543774945280266E-2</v>
+      </c>
+      <c r="N13" s="4">
+        <v>3.3235244554846603E-2</v>
+      </c>
+      <c r="O13" s="4">
+        <v>2.7359735959223905E-2</v>
+      </c>
+      <c r="P13" s="4">
+        <v>2.4946785276220847E-2</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>3.0235621131842236E-2</v>
+      </c>
+      <c r="R13" s="4">
+        <v>1.9223861982193245E-2</v>
+      </c>
+      <c r="S13" s="4">
+        <v>2.3172397645612637E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2080</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1.5308305636434913E-2</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1.6955246823871412E-2</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2.3737904213674371E-2</v>
+      </c>
+      <c r="E14" s="4">
+        <v>9.5249793174312768E-3</v>
+      </c>
+      <c r="F14" s="4">
+        <v>2.1007838025393254E-2</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1.1206676042353689E-2</v>
+      </c>
+      <c r="H14" s="4">
+        <v>2.4999999999999988E-2</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1.264656739597708E-2</v>
+      </c>
+      <c r="J14" s="4">
+        <v>2.0233119344277139E-2</v>
+      </c>
+      <c r="K14" s="4">
+        <v>2.2230487633433695E-2</v>
+      </c>
+      <c r="L14" s="4">
+        <v>3.2396265710841914E-2</v>
+      </c>
+      <c r="M14" s="4">
+        <v>2.1917558974578037E-2</v>
+      </c>
+      <c r="N14" s="4">
+        <v>3.2312043317211978E-2</v>
+      </c>
+      <c r="O14" s="4">
+        <v>2.6599743293689908E-2</v>
+      </c>
+      <c r="P14" s="4">
+        <v>2.4253819018548048E-2</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>2.9395742767068841E-2</v>
+      </c>
+      <c r="R14" s="4">
+        <v>1.8689865816021209E-2</v>
+      </c>
+      <c r="S14" s="4">
+        <v>2.252871993323451E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2085</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1.4870925475393915E-2</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1.6520792821890194E-2</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2.3059678378997958E-2</v>
+      </c>
+      <c r="E15" s="4">
+        <v>9.2528370512189543E-3</v>
+      </c>
+      <c r="F15" s="4">
+        <v>2.0407614081810591E-2</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1.088648529828644E-2</v>
+      </c>
+      <c r="H15" s="4">
+        <v>2.4285714285714272E-2</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1.2285236898949163E-2</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1.9655030220154933E-2</v>
+      </c>
+      <c r="K15" s="4">
+        <v>2.1595330843907017E-2</v>
+      </c>
+      <c r="L15" s="4">
+        <v>3.1470658119103573E-2</v>
+      </c>
+      <c r="M15" s="4">
+        <v>2.1291343003875807E-2</v>
+      </c>
+      <c r="N15" s="4">
+        <v>3.1388842079577352E-2</v>
+      </c>
+      <c r="O15" s="4">
+        <v>2.5839750628155911E-2</v>
+      </c>
+      <c r="P15" s="4">
+        <v>2.3560852760875248E-2</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>2.8555864402295447E-2</v>
+      </c>
+      <c r="R15" s="4">
+        <v>1.8155869649849173E-2</v>
+      </c>
+      <c r="S15" s="4">
+        <v>2.1885042220856382E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2090</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1.4433545314352918E-2</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1.5645393666086672E-2</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2.2381452544321546E-2</v>
+      </c>
+      <c r="E16" s="4">
+        <v>8.9806947850066318E-3</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1.9807390138227927E-2</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1.0566294554219192E-2</v>
+      </c>
+      <c r="H16" s="4">
+        <v>2.3571428571428556E-2</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1.1923906401921246E-2</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1.9076941096032727E-2</v>
+      </c>
+      <c r="K16" s="4">
+        <v>2.0960174054380339E-2</v>
+      </c>
+      <c r="L16" s="4">
+        <v>3.0545050527365232E-2</v>
+      </c>
+      <c r="M16" s="4">
+        <v>2.0665127033173577E-2</v>
+      </c>
+      <c r="N16" s="4">
+        <v>3.0465640841942723E-2</v>
+      </c>
+      <c r="O16" s="4">
+        <v>2.5079757962621914E-2</v>
+      </c>
+      <c r="P16" s="4">
+        <v>2.2867886503202449E-2</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>2.7715986037522053E-2</v>
+      </c>
+      <c r="R16" s="4">
+        <v>1.7621873483677136E-2</v>
+      </c>
+      <c r="S16" s="4">
+        <v>2.1241364508478255E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2095</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1.399616515331192E-2</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1.525459629557321E-2</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2.1703226709645133E-2</v>
+      </c>
+      <c r="E17" s="4">
+        <v>8.7085525187943092E-3</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1.9207166194645263E-2</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1.0246103810151943E-2</v>
+      </c>
+      <c r="H17" s="4">
+        <v>2.285714285714284E-2</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1.1562575904893329E-2</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1.8498851971910521E-2</v>
+      </c>
+      <c r="K17" s="4">
+        <v>2.0325017264853661E-2</v>
+      </c>
+      <c r="L17" s="4">
+        <v>2.9619442935626891E-2</v>
+      </c>
+      <c r="M17" s="4">
+        <v>2.0038911062471347E-2</v>
+      </c>
+      <c r="N17" s="4">
+        <v>2.9542439604308093E-2</v>
+      </c>
+      <c r="O17" s="4">
+        <v>2.4319765297087917E-2</v>
+      </c>
+      <c r="P17" s="4">
+        <v>2.2174920245529649E-2</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>2.6876107672748659E-2</v>
+      </c>
+      <c r="R17" s="4">
+        <v>1.70878773175051E-2</v>
+      </c>
+      <c r="S17" s="4">
+        <v>2.0597686796100127E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2100</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1.3558784992270922E-2</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1.4777890161336547E-2</v>
+      </c>
+      <c r="D18" s="4">
+        <v>2.1025000874968721E-2</v>
+      </c>
+      <c r="E18" s="4">
+        <v>8.4364102525819867E-3</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1.8606942251062599E-2</v>
+      </c>
+      <c r="G18" s="4">
+        <v>9.9259130660846948E-3</v>
+      </c>
+      <c r="H18" s="4">
+        <v>2.2142857142857124E-2</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1.1201245407865412E-2</v>
+      </c>
+      <c r="J18" s="4">
+        <v>1.7920762847788315E-2</v>
+      </c>
+      <c r="K18" s="4">
+        <v>1.9689860475326983E-2</v>
+      </c>
+      <c r="L18" s="4">
+        <v>2.869383534388855E-2</v>
+      </c>
+      <c r="M18" s="4">
+        <v>1.9412695091769117E-2</v>
+      </c>
+      <c r="N18" s="4">
+        <v>2.8619238366673464E-2</v>
+      </c>
+      <c r="O18" s="4">
+        <v>2.355977263155392E-2</v>
+      </c>
+      <c r="P18" s="4">
+        <v>2.148195398785685E-2</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>2.6036229307975264E-2</v>
+      </c>
+      <c r="R18" s="4">
+        <v>1.6553881151333064E-2</v>
+      </c>
+      <c r="S18" s="4">
+        <v>1.9954009083722E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8E5F6BA-902F-4B20-BCC8-F44B01010D69}">
+  <dimension ref="A1:S19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2">
+        <v>210.70400000000001</v>
+      </c>
+      <c r="C2">
+        <v>39.178000000000004</v>
+      </c>
+      <c r="D2">
+        <v>1428.25</v>
+      </c>
+      <c r="E2">
+        <v>1432.8520000000001</v>
+      </c>
+      <c r="F2">
+        <v>124.68600000000001</v>
+      </c>
+      <c r="G2">
+        <v>51.751999999999995</v>
+      </c>
+      <c r="H2">
+        <v>129.38999999999999</v>
+      </c>
+      <c r="I2">
+        <v>145.28399999999999</v>
+      </c>
+      <c r="J2">
+        <v>343.47800000000001</v>
+      </c>
+      <c r="K2">
+        <v>316.60400000000004</v>
+      </c>
+      <c r="L2">
+        <v>532.98400000000004</v>
+      </c>
+      <c r="M2">
+        <v>252.68799999999999</v>
+      </c>
+      <c r="N2">
+        <v>250.09800000000001</v>
+      </c>
+      <c r="O2">
+        <v>721.78200000000004</v>
+      </c>
+      <c r="P2">
+        <v>45.346000000000004</v>
+      </c>
+      <c r="Q2">
+        <v>286.39999999999998</v>
+      </c>
+      <c r="R2">
+        <v>1465.134</v>
+      </c>
+      <c r="S2">
+        <v>280.27199999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>212.42</v>
+      </c>
+      <c r="C3">
+        <v>39.950000000000003</v>
+      </c>
+      <c r="D3">
+        <v>1425.13</v>
+      </c>
+      <c r="E3">
+        <v>1457.44</v>
+      </c>
+      <c r="F3">
+        <v>123.43</v>
+      </c>
+      <c r="G3">
+        <v>51.7</v>
+      </c>
+      <c r="H3">
+        <v>131.41</v>
+      </c>
+      <c r="I3">
+        <v>144.44</v>
+      </c>
+      <c r="J3">
+        <v>346.37</v>
+      </c>
+      <c r="K3">
+        <v>321.3</v>
+      </c>
+      <c r="L3">
+        <v>534.82000000000005</v>
+      </c>
+      <c r="M3">
+        <v>253.4</v>
+      </c>
+      <c r="N3">
+        <v>252.75</v>
+      </c>
+      <c r="O3">
+        <v>739.37</v>
+      </c>
+      <c r="P3">
+        <v>46.35</v>
+      </c>
+      <c r="Q3">
+        <v>297.86</v>
+      </c>
+      <c r="R3">
+        <v>1532.37</v>
+      </c>
+      <c r="S3">
+        <v>284.62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2030</v>
+      </c>
+      <c r="B4">
+        <v>215.81</v>
+      </c>
+      <c r="C4">
+        <v>41.52</v>
+      </c>
+      <c r="D4">
+        <v>1407.55</v>
+      </c>
+      <c r="E4">
+        <v>1519.36</v>
+      </c>
+      <c r="F4">
+        <v>119.95</v>
+      </c>
+      <c r="G4">
+        <v>51.26</v>
+      </c>
+      <c r="H4">
+        <v>136.44</v>
+      </c>
+      <c r="I4">
+        <v>142.09</v>
+      </c>
+      <c r="J4">
+        <v>354.86</v>
+      </c>
+      <c r="K4">
+        <v>333.1</v>
+      </c>
+      <c r="L4">
+        <v>532.35</v>
+      </c>
+      <c r="M4">
+        <v>260.51</v>
+      </c>
+      <c r="N4">
+        <v>258.66000000000003</v>
+      </c>
+      <c r="O4">
+        <v>784.94</v>
+      </c>
+      <c r="P4">
+        <v>48.84</v>
+      </c>
+      <c r="Q4">
+        <v>323.2</v>
+      </c>
+      <c r="R4">
+        <v>1709.22</v>
+      </c>
+      <c r="S4">
+        <v>294.94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2035</v>
+      </c>
+      <c r="B5">
+        <v>218.04</v>
+      </c>
+      <c r="C5">
+        <v>42.8</v>
+      </c>
+      <c r="D5">
+        <v>1383.29</v>
+      </c>
+      <c r="E5">
+        <v>1573.78</v>
+      </c>
+      <c r="F5">
+        <v>116.25</v>
+      </c>
+      <c r="G5">
+        <v>50.41</v>
+      </c>
+      <c r="H5">
+        <v>140.76</v>
+      </c>
+      <c r="I5">
+        <v>140.09</v>
+      </c>
+      <c r="J5">
+        <v>362.55</v>
+      </c>
+      <c r="K5">
+        <v>343.39</v>
+      </c>
+      <c r="L5">
+        <v>529.13</v>
+      </c>
+      <c r="M5">
+        <v>265.20999999999998</v>
+      </c>
+      <c r="N5">
+        <v>263.79000000000002</v>
+      </c>
+      <c r="O5">
+        <v>831.29</v>
+      </c>
+      <c r="P5">
+        <v>51.13</v>
+      </c>
+      <c r="Q5">
+        <v>345.94</v>
+      </c>
+      <c r="R5">
+        <v>1891.25</v>
+      </c>
+      <c r="S5">
+        <v>303.77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2040</v>
+      </c>
+      <c r="B6">
+        <v>219.19</v>
+      </c>
+      <c r="C6">
+        <v>43.86</v>
+      </c>
+      <c r="D6">
+        <v>1353.01</v>
+      </c>
+      <c r="E6">
+        <v>1618.71</v>
+      </c>
+      <c r="F6">
+        <v>112.53</v>
+      </c>
+      <c r="G6">
+        <v>49.1</v>
+      </c>
+      <c r="H6">
+        <v>144.32</v>
+      </c>
+      <c r="I6">
+        <v>138.41999999999999</v>
+      </c>
+      <c r="J6">
+        <v>369.57</v>
+      </c>
+      <c r="K6">
+        <v>351.9</v>
+      </c>
+      <c r="L6">
+        <v>524.91999999999996</v>
+      </c>
+      <c r="M6">
+        <v>269.44</v>
+      </c>
+      <c r="N6">
+        <v>267.74</v>
+      </c>
+      <c r="O6">
+        <v>875.37</v>
+      </c>
+      <c r="P6">
+        <v>53.32</v>
+      </c>
+      <c r="Q6">
+        <v>367.97</v>
+      </c>
+      <c r="R6">
+        <v>2076.98</v>
+      </c>
+      <c r="S6">
+        <v>311.16000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2045</v>
+      </c>
+      <c r="B7">
+        <v>219.12</v>
+      </c>
+      <c r="C7">
+        <v>44.76</v>
+      </c>
+      <c r="D7">
+        <v>1316.69</v>
+      </c>
+      <c r="E7">
+        <v>1653.23</v>
+      </c>
+      <c r="F7">
+        <v>108.91</v>
+      </c>
+      <c r="G7">
+        <v>47.42</v>
+      </c>
+      <c r="H7">
+        <v>147.02000000000001</v>
+      </c>
+      <c r="I7">
+        <v>137.24</v>
+      </c>
+      <c r="J7">
+        <v>375.58</v>
+      </c>
+      <c r="K7">
+        <v>358.36</v>
+      </c>
+      <c r="L7">
+        <v>519.91999999999996</v>
+      </c>
+      <c r="M7">
+        <v>273.33</v>
+      </c>
+      <c r="N7">
+        <v>270.11</v>
+      </c>
+      <c r="O7">
+        <v>916.55</v>
+      </c>
+      <c r="P7">
+        <v>55.44</v>
+      </c>
+      <c r="Q7">
+        <v>389.13</v>
+      </c>
+      <c r="R7">
+        <v>2263.67</v>
+      </c>
+      <c r="S7">
+        <v>316.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2050</v>
+      </c>
+      <c r="B8">
+        <v>217.7</v>
+      </c>
+      <c r="C8">
+        <v>45.55</v>
+      </c>
+      <c r="D8">
+        <v>1271.58</v>
+      </c>
+      <c r="E8">
+        <v>1677.69</v>
+      </c>
+      <c r="F8">
+        <v>105.46</v>
+      </c>
+      <c r="G8">
+        <v>45.37</v>
+      </c>
+      <c r="H8">
+        <v>148.82</v>
+      </c>
+      <c r="I8">
+        <v>136.26</v>
+      </c>
+      <c r="J8">
+        <v>380.41</v>
+      </c>
+      <c r="K8">
+        <v>362.79</v>
+      </c>
+      <c r="L8">
+        <v>513.52</v>
+      </c>
+      <c r="M8">
+        <v>276.44</v>
+      </c>
+      <c r="N8">
+        <v>270.63</v>
+      </c>
+      <c r="O8">
+        <v>954.53</v>
+      </c>
+      <c r="P8">
+        <v>57.49</v>
+      </c>
+      <c r="Q8">
+        <v>409.11</v>
+      </c>
+      <c r="R8">
+        <v>2448.4</v>
+      </c>
+      <c r="S8">
+        <v>320.45999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2055</v>
+      </c>
+      <c r="B9">
+        <v>215.12</v>
+      </c>
+      <c r="C9">
+        <v>46.28</v>
+      </c>
+      <c r="D9">
+        <v>1214.4100000000001</v>
+      </c>
+      <c r="E9">
+        <v>1693.27</v>
+      </c>
+      <c r="F9">
+        <v>102.07</v>
+      </c>
+      <c r="G9">
+        <v>42.9</v>
+      </c>
+      <c r="H9">
+        <v>149.75</v>
+      </c>
+      <c r="I9">
+        <v>134.82</v>
+      </c>
+      <c r="J9">
+        <v>384.52</v>
+      </c>
+      <c r="K9">
+        <v>365.28</v>
+      </c>
+      <c r="L9">
+        <v>505.45</v>
+      </c>
+      <c r="M9">
+        <v>278.16000000000003</v>
+      </c>
+      <c r="N9">
+        <v>269.27</v>
+      </c>
+      <c r="O9">
+        <v>988.46</v>
+      </c>
+      <c r="P9">
+        <v>59.4</v>
+      </c>
+      <c r="Q9">
+        <v>427.67</v>
+      </c>
+      <c r="R9">
+        <v>2629.27</v>
+      </c>
+      <c r="S9">
+        <v>322.26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2060</v>
+      </c>
+      <c r="B10">
+        <v>211.46</v>
+      </c>
+      <c r="C10">
+        <v>47.06</v>
+      </c>
+      <c r="D10">
+        <v>1147.3399999999999</v>
+      </c>
+      <c r="E10">
+        <v>1700.69</v>
+      </c>
+      <c r="F10">
+        <v>98.48</v>
+      </c>
+      <c r="G10">
+        <v>40.14</v>
+      </c>
+      <c r="H10">
+        <v>149.91999999999999</v>
+      </c>
+      <c r="I10">
+        <v>133.06</v>
+      </c>
+      <c r="J10">
+        <v>388.51</v>
+      </c>
+      <c r="K10">
+        <v>365.86</v>
+      </c>
+      <c r="L10">
+        <v>495.88</v>
+      </c>
+      <c r="M10">
+        <v>278.52999999999997</v>
+      </c>
+      <c r="N10">
+        <v>266.42</v>
+      </c>
+      <c r="O10">
+        <v>1018.84</v>
+      </c>
+      <c r="P10">
+        <v>61.2</v>
+      </c>
+      <c r="Q10">
+        <v>444.5</v>
+      </c>
+      <c r="R10">
+        <v>2804.4</v>
+      </c>
+      <c r="S10">
+        <v>322.57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2065</v>
+      </c>
+      <c r="B11">
+        <v>206.85</v>
+      </c>
+      <c r="C11">
+        <v>47.92</v>
+      </c>
+      <c r="D11">
+        <v>1077.3</v>
+      </c>
+      <c r="E11">
+        <v>1699.89</v>
+      </c>
+      <c r="F11">
+        <v>94.71</v>
+      </c>
+      <c r="G11">
+        <v>37.36</v>
+      </c>
+      <c r="H11">
+        <v>149.4</v>
+      </c>
+      <c r="I11">
+        <v>131.35</v>
+      </c>
+      <c r="J11">
+        <v>392.89</v>
+      </c>
+      <c r="K11">
+        <v>364.72</v>
+      </c>
+      <c r="L11">
+        <v>486.15</v>
+      </c>
+      <c r="M11">
+        <v>277.86</v>
+      </c>
+      <c r="N11">
+        <v>262.57</v>
+      </c>
+      <c r="O11">
+        <v>1044.96</v>
+      </c>
+      <c r="P11">
+        <v>62.89</v>
+      </c>
+      <c r="Q11">
+        <v>459.58</v>
+      </c>
+      <c r="R11">
+        <v>2972</v>
+      </c>
+      <c r="S11">
+        <v>321.81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2070</v>
+      </c>
+      <c r="B12">
+        <v>201.47</v>
+      </c>
+      <c r="C12">
+        <v>48.78</v>
+      </c>
+      <c r="D12">
+        <v>1009.67</v>
+      </c>
+      <c r="E12">
+        <v>1690.65</v>
+      </c>
+      <c r="F12">
+        <v>90.97</v>
+      </c>
+      <c r="G12">
+        <v>34.71</v>
+      </c>
+      <c r="H12">
+        <v>148.22</v>
+      </c>
+      <c r="I12">
+        <v>129.85</v>
+      </c>
+      <c r="J12">
+        <v>397.74</v>
+      </c>
+      <c r="K12">
+        <v>361.98</v>
+      </c>
+      <c r="L12">
+        <v>477.13</v>
+      </c>
+      <c r="M12">
+        <v>276.47000000000003</v>
+      </c>
+      <c r="N12">
+        <v>257.99</v>
+      </c>
+      <c r="O12">
+        <v>1066.92</v>
+      </c>
+      <c r="P12">
+        <v>64.540000000000006</v>
+      </c>
+      <c r="Q12">
+        <v>472.75</v>
+      </c>
+      <c r="R12">
+        <v>3130.05</v>
+      </c>
+      <c r="S12">
+        <v>320.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2075</v>
+      </c>
+      <c r="B13">
+        <v>195.51</v>
+      </c>
+      <c r="C13">
+        <v>49.58</v>
+      </c>
+      <c r="D13">
+        <v>944.78</v>
+      </c>
+      <c r="E13">
+        <v>1673.08</v>
+      </c>
+      <c r="F13">
+        <v>87.65</v>
+      </c>
+      <c r="G13">
+        <v>32.21</v>
+      </c>
+      <c r="H13">
+        <v>146.43</v>
+      </c>
+      <c r="I13">
+        <v>128.65</v>
+      </c>
+      <c r="J13">
+        <v>402.44</v>
+      </c>
+      <c r="K13">
+        <v>357.76</v>
+      </c>
+      <c r="L13">
+        <v>469.08</v>
+      </c>
+      <c r="M13">
+        <v>274.52999999999997</v>
+      </c>
+      <c r="N13">
+        <v>252.74</v>
+      </c>
+      <c r="O13">
+        <v>1084.27</v>
+      </c>
+      <c r="P13">
+        <v>66.069999999999993</v>
+      </c>
+      <c r="Q13">
+        <v>484.17</v>
+      </c>
+      <c r="R13">
+        <v>3277.3</v>
+      </c>
+      <c r="S13">
+        <v>317.95999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2080</v>
+      </c>
+      <c r="B14">
+        <v>189.24</v>
+      </c>
+      <c r="C14">
+        <v>50.37</v>
+      </c>
+      <c r="D14">
+        <v>880.2</v>
+      </c>
+      <c r="E14">
+        <v>1648.38</v>
+      </c>
+      <c r="F14">
+        <v>84.97</v>
+      </c>
+      <c r="G14">
+        <v>29.89</v>
+      </c>
+      <c r="H14">
+        <v>144.07</v>
+      </c>
+      <c r="I14">
+        <v>127.89</v>
+      </c>
+      <c r="J14">
+        <v>406.71</v>
+      </c>
+      <c r="K14">
+        <v>352.13</v>
+      </c>
+      <c r="L14">
+        <v>461.96</v>
+      </c>
+      <c r="M14">
+        <v>272.17</v>
+      </c>
+      <c r="N14">
+        <v>246.7</v>
+      </c>
+      <c r="O14">
+        <v>1096.6099999999999</v>
+      </c>
+      <c r="P14">
+        <v>67.53</v>
+      </c>
+      <c r="Q14">
+        <v>493.96</v>
+      </c>
+      <c r="R14">
+        <v>3412.07</v>
+      </c>
+      <c r="S14">
+        <v>314.89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2085</v>
+      </c>
+      <c r="B15">
+        <v>182.82</v>
+      </c>
+      <c r="C15">
+        <v>51.14</v>
+      </c>
+      <c r="D15">
+        <v>815.52</v>
+      </c>
+      <c r="E15">
+        <v>1618.14</v>
+      </c>
+      <c r="F15">
+        <v>82.77</v>
+      </c>
+      <c r="G15">
+        <v>27.72</v>
+      </c>
+      <c r="H15">
+        <v>141.21</v>
+      </c>
+      <c r="I15">
+        <v>127.47</v>
+      </c>
+      <c r="J15">
+        <v>410.5</v>
+      </c>
+      <c r="K15">
+        <v>345.28</v>
+      </c>
+      <c r="L15">
+        <v>455.58</v>
+      </c>
+      <c r="M15">
+        <v>269.44</v>
+      </c>
+      <c r="N15">
+        <v>239.98</v>
+      </c>
+      <c r="O15">
+        <v>1104.4100000000001</v>
+      </c>
+      <c r="P15">
+        <v>68.92</v>
+      </c>
+      <c r="Q15">
+        <v>502.9</v>
+      </c>
+      <c r="R15">
+        <v>3532.78</v>
+      </c>
+      <c r="S15">
+        <v>311.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2090</v>
+      </c>
+      <c r="B16">
+        <v>176.42</v>
+      </c>
+      <c r="C16">
+        <v>51.89</v>
+      </c>
+      <c r="D16">
+        <v>753.52</v>
+      </c>
+      <c r="E16">
+        <v>1583.91</v>
+      </c>
+      <c r="F16">
+        <v>80.819999999999993</v>
+      </c>
+      <c r="G16">
+        <v>25.65</v>
+      </c>
+      <c r="H16">
+        <v>137.94</v>
+      </c>
+      <c r="I16">
+        <v>127.17</v>
+      </c>
+      <c r="J16">
+        <v>414.1</v>
+      </c>
+      <c r="K16">
+        <v>337.45</v>
+      </c>
+      <c r="L16">
+        <v>449.63</v>
+      </c>
+      <c r="M16">
+        <v>266.33999999999997</v>
+      </c>
+      <c r="N16">
+        <v>232.86</v>
+      </c>
+      <c r="O16">
+        <v>1108.18</v>
+      </c>
+      <c r="P16">
+        <v>70.28</v>
+      </c>
+      <c r="Q16">
+        <v>510.79</v>
+      </c>
+      <c r="R16">
+        <v>3639.29</v>
+      </c>
+      <c r="S16">
+        <v>306.60000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2095</v>
+      </c>
+      <c r="B17">
+        <v>170.11</v>
+      </c>
+      <c r="C17">
+        <v>52.65</v>
+      </c>
+      <c r="D17">
+        <v>695.67</v>
+      </c>
+      <c r="E17">
+        <v>1547.14</v>
+      </c>
+      <c r="F17">
+        <v>78.94</v>
+      </c>
+      <c r="G17">
+        <v>23.72</v>
+      </c>
+      <c r="H17">
+        <v>134.38</v>
+      </c>
+      <c r="I17">
+        <v>126.88</v>
+      </c>
+      <c r="J17">
+        <v>417.76</v>
+      </c>
+      <c r="K17">
+        <v>329.04</v>
+      </c>
+      <c r="L17">
+        <v>444</v>
+      </c>
+      <c r="M17">
+        <v>262.89999999999998</v>
+      </c>
+      <c r="N17">
+        <v>225.68</v>
+      </c>
+      <c r="O17">
+        <v>1108.7</v>
+      </c>
+      <c r="P17">
+        <v>71.62</v>
+      </c>
+      <c r="Q17">
+        <v>517.52</v>
+      </c>
+      <c r="R17">
+        <v>3730.45</v>
+      </c>
+      <c r="S17">
+        <v>301.52999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2100</v>
+      </c>
+      <c r="B18">
+        <v>163.97</v>
+      </c>
+      <c r="C18">
+        <v>53.52</v>
+      </c>
+      <c r="D18">
+        <v>640.79</v>
+      </c>
+      <c r="E18">
+        <v>1509.11</v>
+      </c>
+      <c r="F18">
+        <v>77.040000000000006</v>
+      </c>
+      <c r="G18">
+        <v>22.01</v>
+      </c>
+      <c r="H18">
+        <v>130.63</v>
+      </c>
+      <c r="I18">
+        <v>126.44</v>
+      </c>
+      <c r="J18">
+        <v>421.01</v>
+      </c>
+      <c r="K18">
+        <v>320.33</v>
+      </c>
+      <c r="L18">
+        <v>438.18</v>
+      </c>
+      <c r="M18">
+        <v>259.10000000000002</v>
+      </c>
+      <c r="N18">
+        <v>218.67</v>
+      </c>
+      <c r="O18">
+        <v>1105.69</v>
+      </c>
+      <c r="P18">
+        <v>72.83</v>
+      </c>
+      <c r="Q18">
+        <v>522.91</v>
+      </c>
+      <c r="R18">
+        <v>3807.04</v>
+      </c>
+      <c r="S18">
+        <v>296.07</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>2105</v>
+      </c>
+      <c r="B19" s="5">
+        <f>B18</f>
+        <v>163.97</v>
+      </c>
+      <c r="C19" s="5">
+        <f t="shared" ref="C19:S19" si="0">C18</f>
+        <v>53.52</v>
+      </c>
+      <c r="D19" s="5">
+        <f t="shared" si="0"/>
+        <v>640.79</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="0"/>
+        <v>1509.11</v>
+      </c>
+      <c r="F19" s="5">
+        <f t="shared" si="0"/>
+        <v>77.040000000000006</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" si="0"/>
+        <v>22.01</v>
+      </c>
+      <c r="H19" s="5">
+        <f t="shared" si="0"/>
+        <v>130.63</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>126.44</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" si="0"/>
+        <v>421.01</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" si="0"/>
+        <v>320.33</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="0"/>
+        <v>438.18</v>
+      </c>
+      <c r="M19" s="5">
+        <f t="shared" si="0"/>
+        <v>259.10000000000002</v>
+      </c>
+      <c r="N19" s="5">
+        <f t="shared" si="0"/>
+        <v>218.67</v>
+      </c>
+      <c r="O19" s="5">
+        <f t="shared" si="0"/>
+        <v>1105.69</v>
+      </c>
+      <c r="P19" s="5">
+        <f t="shared" si="0"/>
+        <v>72.83</v>
+      </c>
+      <c r="Q19" s="5">
+        <f t="shared" si="0"/>
+        <v>522.91</v>
+      </c>
+      <c r="R19" s="5">
+        <f t="shared" si="0"/>
+        <v>3807.04</v>
+      </c>
+      <c r="S19" s="5">
+        <f t="shared" si="0"/>
+        <v>296.07</v>
       </c>
     </row>
   </sheetData>
